--- a/leads/sabusinessdirectories_contacts.xlsx
+++ b/leads/sabusinessdirectories_contacts.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manu\Documents\Web dev\Projects\unlimited_webscraper\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manu\Documents\Web dev\Projects\unlimited_webscraper\leads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -920,6 +920,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B95"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="48" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
